--- a/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
+++ b/InputData/hydgn/BHPSbP/BAU Hydrogen Production Shr by Pathway.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\hydgn\BHPSbP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndonesiaEPS/Shared Documents/Updated Indonesia InputData files/hydgn/BHPSbP/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_D1F34EA1E5A9E4844E7ED26FA02AC4020B0C06F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{68978242-235B-4F79-BE3D-393BA42EAA7E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25815" windowHeight="11970"/>
+    <workbookView xWindow="43095" yWindow="1080" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="BHPSbP" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>BHPSbP BAU Hydrogen Production Shares by Pathway</t>
   </si>
@@ -81,16 +93,25 @@
     <t>We assume today's shares are constant in the BAU case.</t>
   </si>
   <si>
-    <t>thermochemical water splitting</t>
-  </si>
-  <si>
     <t>Production Share (dimensionless)</t>
+  </si>
+  <si>
+    <t>hydrocarbon partial oxidation</t>
+  </si>
+  <si>
+    <t>electrolysis with guaranteed clean electricity</t>
+  </si>
+  <si>
+    <t>natural gas reforming with CCS</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -137,7 +158,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -147,6 +168,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -427,19 +449,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="1" max="1" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -447,62 +469,62 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="3">
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B6" s="4" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B19" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>0.02</v>
       </c>
@@ -510,7 +532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>0.76</v>
       </c>
@@ -518,7 +540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24">
         <f>0.22</f>
         <v>0.22</v>
@@ -529,8 +551,8 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1"/>
-    <hyperlink ref="B19" r:id="rId2"/>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -538,19 +560,19 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AI6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AI8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.1328125" customWidth="1"/>
+    <col min="1" max="1" width="30.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2">
         <v>2017</v>
@@ -655,7 +677,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -667,7 +689,7 @@
         <v>0.05</v>
       </c>
       <c r="D2">
-        <f t="shared" ref="D2:AI6" si="0">$B2</f>
+        <f t="shared" ref="D2:AI8" si="0">$B2</f>
         <v>0.05</v>
       </c>
       <c r="E2">
@@ -795,7 +817,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -935,127 +957,98 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <f t="shared" si="0"/>
+      <c r="B4" s="5">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5">
+        <v>0</v>
+      </c>
+      <c r="M4" s="5">
+        <v>0</v>
+      </c>
+      <c r="N4" s="5">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5">
+        <v>0</v>
+      </c>
+      <c r="P4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>0</v>
+      </c>
+      <c r="R4" s="5">
+        <v>0</v>
+      </c>
+      <c r="S4" s="5">
+        <v>0</v>
+      </c>
+      <c r="T4" s="5">
+        <v>0</v>
+      </c>
+      <c r="U4" s="5">
+        <v>0</v>
+      </c>
+      <c r="V4" s="5">
+        <v>0</v>
+      </c>
+      <c r="W4" s="5">
+        <v>0</v>
+      </c>
+      <c r="X4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="5">
         <v>0</v>
       </c>
       <c r="AF4">
@@ -1075,127 +1068,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <f t="shared" si="0"/>
+      <c r="B5" s="5">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="5">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5">
+        <v>0</v>
+      </c>
+      <c r="P5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>0</v>
+      </c>
+      <c r="R5" s="5">
+        <v>0</v>
+      </c>
+      <c r="S5" s="5">
+        <v>0</v>
+      </c>
+      <c r="T5" s="5">
+        <v>0</v>
+      </c>
+      <c r="U5" s="5">
+        <v>0</v>
+      </c>
+      <c r="V5" s="5">
+        <v>0</v>
+      </c>
+      <c r="W5" s="5">
+        <v>0</v>
+      </c>
+      <c r="X5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
         <v>0</v>
       </c>
       <c r="AF5">
@@ -1215,127 +1179,98 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="V6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="X6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Y6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="Z6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5">
+        <v>0</v>
+      </c>
+      <c r="M6" s="5">
+        <v>0</v>
+      </c>
+      <c r="N6" s="5">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5">
+        <v>0</v>
+      </c>
+      <c r="P6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>0</v>
+      </c>
+      <c r="R6" s="5">
+        <v>0</v>
+      </c>
+      <c r="S6" s="5">
+        <v>0</v>
+      </c>
+      <c r="T6" s="5">
+        <v>0</v>
+      </c>
+      <c r="U6" s="5">
+        <v>0</v>
+      </c>
+      <c r="V6" s="5">
+        <v>0</v>
+      </c>
+      <c r="W6" s="5">
+        <v>0</v>
+      </c>
+      <c r="X6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="5">
         <v>0</v>
       </c>
       <c r="AF6">
@@ -1351,6 +1286,228 @@
         <v>0</v>
       </c>
       <c r="AI6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5">
+        <v>0</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5">
+        <v>0</v>
+      </c>
+      <c r="M7" s="5">
+        <v>0</v>
+      </c>
+      <c r="N7" s="5">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5">
+        <v>0</v>
+      </c>
+      <c r="P7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>0</v>
+      </c>
+      <c r="R7" s="5">
+        <v>0</v>
+      </c>
+      <c r="S7" s="5">
+        <v>0</v>
+      </c>
+      <c r="T7" s="5">
+        <v>0</v>
+      </c>
+      <c r="U7" s="5">
+        <v>0</v>
+      </c>
+      <c r="V7" s="5">
+        <v>0</v>
+      </c>
+      <c r="W7" s="5">
+        <v>0</v>
+      </c>
+      <c r="X7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5">
+        <v>0</v>
+      </c>
+      <c r="M8" s="5">
+        <v>0</v>
+      </c>
+      <c r="N8" s="5">
+        <v>0</v>
+      </c>
+      <c r="O8" s="5">
+        <v>0</v>
+      </c>
+      <c r="P8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>0</v>
+      </c>
+      <c r="R8" s="5">
+        <v>0</v>
+      </c>
+      <c r="S8" s="5">
+        <v>0</v>
+      </c>
+      <c r="T8" s="5">
+        <v>0</v>
+      </c>
+      <c r="U8" s="5">
+        <v>0</v>
+      </c>
+      <c r="V8" s="5">
+        <v>0</v>
+      </c>
+      <c r="W8" s="5">
+        <v>0</v>
+      </c>
+      <c r="X8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="5">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="5">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="AI8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -1358,4 +1515,198 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
+    <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1659011e-6b88-4225-9a61-aaf33aaf19e8" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41180FF7-E08E-45B7-9E04-497E452830EE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5834376C-D11F-45D0-AD69-276CF827D9DC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{448DDF4B-ABFA-42A3-B0EA-4FD9C7DB3106}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>